--- a/data/trans_camb/IP1003-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1003-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 2,47</t>
+          <t>-9,21; 2,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 5,6</t>
+          <t>-6,99; 6,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 2,93</t>
+          <t>-8,23; 2,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 2,58</t>
+          <t>-6,44; 1,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 2,49</t>
+          <t>-6,0; 2,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 10,29</t>
+          <t>-1,58; 9,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 0,78</t>
+          <t>-6,32; 1,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 2,31</t>
+          <t>-5,05; 2,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 5,32</t>
+          <t>-2,96; 5,22</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-83,28; 57,84</t>
+          <t>-79,45; 63,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-67,42; 105,08</t>
+          <t>-64,43; 127,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-75,66; 66,05</t>
+          <t>-73,12; 70,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 148,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-88,1; 191,74</t>
+          <t>-88,79; 170,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-29,49; 548,4</t>
+          <t>-36,17; 453,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-76,34; 30,55</t>
+          <t>-76,5; 35,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-66,99; 54,79</t>
+          <t>-64,61; 60,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-39,82; 126,25</t>
+          <t>-40,05; 118,05</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,62; 0,7</t>
+          <t>-10,36; 0,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,7; -0,08</t>
+          <t>-10,67; -0,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 3,61</t>
+          <t>-8,55; 3,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 1,95</t>
+          <t>-8,89; 2,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 3,97</t>
+          <t>-7,53; 3,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 8,56</t>
+          <t>-4,84; 8,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,15; -0,06</t>
+          <t>-7,67; 0,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 0,32</t>
+          <t>-7,37; 0,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 4,35</t>
+          <t>-5,12; 4,57</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-91,98; 38,7</t>
+          <t>-90,68; 34,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-92,12; 33,59</t>
+          <t>-92,93; 14,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-81,18; 120,47</t>
+          <t>-77,2; 98,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-84,22; 63,94</t>
+          <t>-86,83; 75,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-74,25; 113,36</t>
+          <t>-76,23; 132,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-62,64; 234,21</t>
+          <t>-59,35; 225,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-78,41; 3,51</t>
+          <t>-79,32; 8,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-74,24; 15,19</t>
+          <t>-72,75; 14,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-60,31; 92,05</t>
+          <t>-57,19; 94,46</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 3,31</t>
+          <t>-8,51; 2,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 1,78</t>
+          <t>-9,2; 2,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 10,48</t>
+          <t>-5,36; 9,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,89; -2,59</t>
+          <t>-13,97; -2,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,97; 3,5</t>
+          <t>-10,43; 2,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 9,13</t>
+          <t>-8,32; 9,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,14; -1,44</t>
+          <t>-9,66; -1,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 0,69</t>
+          <t>-8,14; 0,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 6,45</t>
+          <t>-4,98; 6,98</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-86,7; 215,72</t>
+          <t>-88,61; 126,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 134,65</t>
+          <t>-100,0; 145,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-64,01; 470,47</t>
+          <t>-72,23; 528,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -19,75</t>
+          <t>-100,0; -24,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-80,59; 70,52</t>
+          <t>-82,53; 47,28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-74,99; 147,46</t>
+          <t>-74,39; 162,44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-88,49; -19,79</t>
+          <t>-89,83; -22,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-76,75; 19,14</t>
+          <t>-78,12; 24,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-55,83; 115,64</t>
+          <t>-53,45; 135,61</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 2,77</t>
+          <t>-3,94; 2,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 3,89</t>
+          <t>-2,42; 4,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 6,4</t>
+          <t>-1,44; 6,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 8,46</t>
+          <t>0,21; 8,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 2,24</t>
+          <t>-5,05; 2,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 4,75</t>
+          <t>-3,65; 5,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 4,84</t>
+          <t>-0,56; 4,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 2,05</t>
+          <t>-2,77; 2,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 4,44</t>
+          <t>-1,53; 4,36</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-66,41; 112,27</t>
+          <t>-68,21; 92,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-43,59; 161,97</t>
+          <t>-45,47; 167,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-30,64; 211,39</t>
+          <t>-28,31; 248,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 192,79</t>
+          <t>-0,02; 207,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-64,29; 55,3</t>
+          <t>-62,3; 51,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-47,24; 113,93</t>
+          <t>-46,25; 114,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 121,88</t>
+          <t>-9,08; 121,49</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-43,51; 52,05</t>
+          <t>-42,52; 52,7</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-26,91; 105,75</t>
+          <t>-25,08; 106,86</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 6,66</t>
+          <t>-4,75; 6,2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 2,67</t>
+          <t>-7,71; 2,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 1,05</t>
+          <t>-8,68; 1,44</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 5,06</t>
+          <t>-3,71; 5,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 3,63</t>
+          <t>-4,46; 4,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,8; 13,26</t>
+          <t>1,51; 13,36</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 4,68</t>
+          <t>-2,46; 4,4</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 1,92</t>
+          <t>-4,59; 2,2</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 6,74</t>
+          <t>-1,11; 7,0</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-45,96; 150,46</t>
+          <t>-46,47; 135,63</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-72,82; 72,36</t>
+          <t>-70,1; 75,35</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-81,16; 36,62</t>
+          <t>-80,12; 40,8</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-55,36; 214,71</t>
+          <t>-57,72; 217,42</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-67,41; 139,03</t>
+          <t>-69,62; 167,18</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,1; 548,7</t>
+          <t>8,7; 522,46</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-33,56; 121,34</t>
+          <t>-31,91; 110,9</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-56,84; 47,92</t>
+          <t>-59,67; 53,03</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-19,15; 154,34</t>
+          <t>-16,64; 152,44</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 1,82</t>
+          <t>-8,67; 1,49</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 5,54</t>
+          <t>-7,13; 5,22</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 3,93</t>
+          <t>-7,01; 3,9</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-13,44; -0,41</t>
+          <t>-14,58; -0,11</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-11,08; 4,69</t>
+          <t>-11,31; 5,34</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-11,79; 3,95</t>
+          <t>-11,28; 3,97</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-9,22; -0,05</t>
+          <t>-9,82; -0,59</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 2,98</t>
+          <t>-6,97; 3,42</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 2,55</t>
+          <t>-7,14; 1,99</t>
         </is>
       </c>
     </row>
@@ -1868,42 +1868,42 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 393,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-90,63; 273,33</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-91,41; 17,86</t>
+          <t>-90,45; 30,84</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-77,34; 78,06</t>
+          <t>-75,15; 88,74</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-79,03; 60,8</t>
+          <t>-76,49; 67,43</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-88,85; 10,37</t>
+          <t>-88,9; 8,61</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-65,9; 57,51</t>
+          <t>-67,89; 64,71</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-66,6; 57,73</t>
+          <t>-67,71; 47,76</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 0,34</t>
+          <t>-3,8; 0,3</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 0,64</t>
+          <t>-3,62; 0,54</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 1,62</t>
+          <t>-3,01; 1,4</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 1,37</t>
+          <t>-2,91; 1,35</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 0,38</t>
+          <t>-3,81; 0,18</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 4,49</t>
+          <t>-0,49; 4,47</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 0,44</t>
+          <t>-2,49; 0,3</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,04; -0,18</t>
+          <t>-3,07; -0,34</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 2,28</t>
+          <t>-1,01; 2,36</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-49,94; 7,72</t>
+          <t>-50,9; 7,62</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-47,08; 15,84</t>
+          <t>-49,5; 11,41</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-40,58; 31,85</t>
+          <t>-41,92; 27,22</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-37,49; 24,65</t>
+          <t>-37,66; 26,14</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-50,43; 7,93</t>
+          <t>-49,0; 4,27</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-8,37; 81,47</t>
+          <t>-6,77; 77,52</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-35,19; 8,47</t>
+          <t>-35,03; 5,33</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-43,3; -2,26</t>
+          <t>-42,66; -4,72</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-16,36; 40,69</t>
+          <t>-15,28; 42,15</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1003-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1003-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 2,6</t>
+          <t>-8,97; 2,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 6,53</t>
+          <t>-6,74; 5,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 2,9</t>
+          <t>-8,19; 2,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 1,92</t>
+          <t>-6,44; 2,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 2,39</t>
+          <t>-6,31; 2,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 9,95</t>
+          <t>-1,18; 9,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 1,15</t>
+          <t>-6,66; 0,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 2,59</t>
+          <t>-5,26; 2,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 5,22</t>
+          <t>-3,52; 4,87</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-79,45; 63,03</t>
+          <t>-79,56; 71,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-64,43; 127,58</t>
+          <t>-63,8; 114,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-73,12; 70,51</t>
+          <t>-72,63; 75,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 148,64</t>
+          <t>-100,0; 176,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-88,79; 170,18</t>
+          <t>-100,0; 137,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,17; 453,55</t>
+          <t>-30,58; 496,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-76,5; 35,17</t>
+          <t>-77,22; 23,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-64,61; 60,62</t>
+          <t>-66,01; 60,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-40,05; 118,05</t>
+          <t>-42,97; 110,47</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 0,36</t>
+          <t>-10,3; 0,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,67; -0,67</t>
+          <t>-10,77; -0,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 3,3</t>
+          <t>-9,24; 3,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 2,49</t>
+          <t>-8,4; 2,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 3,81</t>
+          <t>-7,4; 4,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 8,3</t>
+          <t>-5,04; 8,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 0,15</t>
+          <t>-7,41; 0,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 0,45</t>
+          <t>-7,3; 0,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 4,57</t>
+          <t>-4,98; 4,08</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-90,68; 34,64</t>
+          <t>-90,65; 40,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-92,93; 14,28</t>
+          <t>-92,35; 18,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-77,2; 98,6</t>
+          <t>-79,63; 95,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-86,83; 75,9</t>
+          <t>-81,77; 89,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-76,23; 132,11</t>
+          <t>-75,99; 123,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-59,35; 225,48</t>
+          <t>-56,93; 216,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-79,32; 8,09</t>
+          <t>-77,43; 9,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-72,75; 14,7</t>
+          <t>-74,77; 12,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-57,19; 94,46</t>
+          <t>-56,23; 85,56</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 2,76</t>
+          <t>-8,87; 2,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 2,27</t>
+          <t>-9,39; 2,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 9,98</t>
+          <t>-6,14; 9,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,97; -2,51</t>
+          <t>-13,3; -2,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 2,14</t>
+          <t>-10,08; 2,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 9,65</t>
+          <t>-8,55; 9,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,66; -1,52</t>
+          <t>-9,62; -1,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 0,98</t>
+          <t>-8,18; 0,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 6,98</t>
+          <t>-5,0; 6,65</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-88,61; 126,3</t>
+          <t>-90,46; 100,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 145,44</t>
+          <t>-100,0; 188,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-72,23; 528,52</t>
+          <t>-79,73; 379,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -24,72</t>
+          <t>-100,0; -22,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-82,53; 47,28</t>
+          <t>-81,83; 46,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-74,39; 162,44</t>
+          <t>-71,76; 159,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-89,83; -22,79</t>
+          <t>-87,41; -9,33</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-78,12; 24,18</t>
+          <t>-78,86; 10,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-53,45; 135,61</t>
+          <t>-53,27; 124,24</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 2,3</t>
+          <t>-3,85; 2,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 4,14</t>
+          <t>-2,26; 4,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 6,67</t>
+          <t>-1,29; 6,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,21; 8,82</t>
+          <t>0,44; 9,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 2,22</t>
+          <t>-5,39; 2,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 5,01</t>
+          <t>-3,69; 5,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 4,71</t>
+          <t>-0,76; 4,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 2,05</t>
+          <t>-2,9; 2,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 4,36</t>
+          <t>-1,3; 4,72</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-68,21; 92,44</t>
+          <t>-67,8; 95,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-45,47; 167,17</t>
+          <t>-39,7; 155,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-28,31; 248,97</t>
+          <t>-24,55; 227,99</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 207,28</t>
+          <t>3,53; 217,86</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-62,3; 51,42</t>
+          <t>-64,15; 55,3</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-46,25; 114,28</t>
+          <t>-48,09; 118,12</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 121,49</t>
+          <t>-12,15; 128,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-42,52; 52,7</t>
+          <t>-44,19; 54,73</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-25,08; 106,86</t>
+          <t>-21,52; 126,59</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 6,2</t>
+          <t>-4,96; 6,24</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 2,81</t>
+          <t>-7,56; 3,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 1,44</t>
+          <t>-8,8; 1,83</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 5,02</t>
+          <t>-3,1; 5,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 4,03</t>
+          <t>-4,13; 4,39</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,51; 13,36</t>
+          <t>1,33; 13,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 4,4</t>
+          <t>-2,24; 4,87</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 2,2</t>
+          <t>-4,1; 2,26</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 7,0</t>
+          <t>-1,11; 6,75</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-46,47; 135,63</t>
+          <t>-48,46; 138,1</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-70,1; 75,35</t>
+          <t>-71,16; 80,36</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-80,12; 40,8</t>
+          <t>-81,0; 50,88</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-57,72; 217,42</t>
+          <t>-53,54; 222,47</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-69,62; 167,18</t>
+          <t>-67,75; 170,16</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,7; 522,46</t>
+          <t>12,05; 521,46</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-31,91; 110,9</t>
+          <t>-29,37; 111,62</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-59,67; 53,03</t>
+          <t>-56,39; 58,71</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-16,64; 152,44</t>
+          <t>-16,39; 158,99</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 1,49</t>
+          <t>-8,37; 1,29</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 5,22</t>
+          <t>-6,76; 4,9</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 3,9</t>
+          <t>-6,91; 3,85</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-14,58; -0,11</t>
+          <t>-14,4; 0,43</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-11,31; 5,34</t>
+          <t>-11,77; 4,29</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 3,97</t>
+          <t>-11,1; 4,49</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-9,82; -0,59</t>
+          <t>-9,35; -0,43</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 3,42</t>
+          <t>-7,3; 2,79</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 1,99</t>
+          <t>-6,94; 1,91</t>
         </is>
       </c>
     </row>
@@ -1868,42 +1868,42 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 279,25</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-90,63; 273,33</t>
+          <t>-88,5; 291,47</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-90,45; 30,84</t>
+          <t>-91,63; 32,65</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-75,15; 88,74</t>
+          <t>-77,78; 65,21</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-76,49; 67,43</t>
+          <t>-73,91; 81,8</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-88,9; 8,61</t>
+          <t>-89,21; 4,56</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-67,89; 64,71</t>
+          <t>-71,78; 51,36</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-67,71; 47,76</t>
+          <t>-70,97; 40,6</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 0,3</t>
+          <t>-3,68; 0,38</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 0,54</t>
+          <t>-3,55; 0,62</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 1,4</t>
+          <t>-2,83; 1,72</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 1,35</t>
+          <t>-2,91; 1,22</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 0,18</t>
+          <t>-3,81; 0,04</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 4,47</t>
+          <t>-0,54; 4,48</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 0,3</t>
+          <t>-2,74; 0,29</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,07; -0,34</t>
+          <t>-3,05; -0,14</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 2,36</t>
+          <t>-0,87; 2,31</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-50,9; 7,62</t>
+          <t>-52,15; 8,13</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-49,5; 11,41</t>
+          <t>-51,08; 13,27</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-41,92; 27,22</t>
+          <t>-38,28; 35,45</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-37,66; 26,14</t>
+          <t>-37,85; 23,05</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-49,0; 4,27</t>
+          <t>-51,26; 0,74</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 77,52</t>
+          <t>-8,16; 75,78</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-35,03; 5,33</t>
+          <t>-37,4; 5,03</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-42,66; -4,72</t>
+          <t>-42,32; -1,33</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-15,28; 42,15</t>
+          <t>-12,16; 39,8</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1003-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1003-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-1,88</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-1,55</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4,68</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-3,47</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-0,86</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-2,69</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,88</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-1,55</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,11</t>
+          <t>-2,14</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>1,32</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 2,86</t>
+          <t>-6,01; 2,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 5,9</t>
+          <t>-6,26; 2,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 2,94</t>
+          <t>-0,69; 11,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 2,25</t>
+          <t>-9,76; 2,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 2,17</t>
+          <t>-7,55; 5,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 9,68</t>
+          <t>-8,59; 3,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 0,64</t>
+          <t>-6,7; 0,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 2,51</t>
+          <t>-5,34; 2,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 4,87</t>
+          <t>-2,76; 6,22</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-45,06%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-37,22%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>112,01%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-41,81%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-10,3%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-32,4%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-45,06%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-37,22%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>-25,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>20,95%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-79,56; 71,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-63,8; 114,89</t>
+          <t>-88,1; 191,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-72,63; 75,8</t>
+          <t>-22,64; 585,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 176,18</t>
+          <t>-83,28; 57,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 137,55</t>
+          <t>-67,42; 105,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-30,58; 496,07</t>
+          <t>-72,79; 84,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-77,22; 23,65</t>
+          <t>-76,34; 30,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-66,01; 60,44</t>
+          <t>-66,99; 54,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-42,97; 110,47</t>
+          <t>-35,56; 138,65</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-2,61</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,56</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,85</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-4,44</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-4,95</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-2,62</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-2,61</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,56</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,19</t>
+          <t>-2,6</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,71</t>
+          <t>-0,43</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,3; 0,58</t>
+          <t>-8,78; 1,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,77; -0,1</t>
+          <t>-7,23; 3,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 3,21</t>
+          <t>-4,97; 10,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 2,78</t>
+          <t>-10,62; 0,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 4,01</t>
+          <t>-10,7; -0,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 8,29</t>
+          <t>-8,58; 3,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 0,09</t>
+          <t>-7,15; -0,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 0,09</t>
+          <t>-7,22; 0,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 4,08</t>
+          <t>-5,01; 4,9</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-38,98%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-23,26%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>27,64%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-58,52%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-65,23%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-34,49%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-38,98%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-23,26%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>-34,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-9,97%</t>
+          <t>-5,95%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-90,65; 40,81</t>
+          <t>-84,22; 63,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-92,35; 18,91</t>
+          <t>-74,25; 113,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-79,63; 95,01</t>
+          <t>-59,12; 261,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-81,77; 89,28</t>
+          <t>-91,98; 38,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-75,99; 123,81</t>
+          <t>-92,12; 33,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,93; 216,66</t>
+          <t>-81,42; 124,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-77,43; 9,27</t>
+          <t>-78,41; 3,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-74,77; 12,16</t>
+          <t>-74,24; 15,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-56,23; 85,56</t>
+          <t>-58,64; 103,26</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-7,55</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-3,78</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-0,87</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-2,4</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-2,87</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,42</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-7,55</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-3,78</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,51</t>
+          <t>1,77</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,14</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 2,31</t>
+          <t>-12,89; -2,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 2,51</t>
+          <t>-9,97; 3,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 9,6</t>
+          <t>-8,49; 8,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,3; -2,49</t>
+          <t>-8,06; 3,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 2,05</t>
+          <t>-9,01; 1,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 9,88</t>
+          <t>-4,32; 11,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,62; -1,61</t>
+          <t>-9,14; -1,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 0,51</t>
+          <t>-7,85; 0,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 6,65</t>
+          <t>-5,39; 6,05</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-81,9%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-41,05%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-9,43%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-41,43%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-49,53%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>24,46%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-81,9%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-41,05%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-5,56%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-90,46; 100,05</t>
+          <t>-100,0; -19,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 188,94</t>
+          <t>-80,59; 70,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-79,73; 379,07</t>
+          <t>-75,85; 140,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -22,89</t>
+          <t>-86,7; 215,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-81,83; 46,87</t>
+          <t>-100,0; 134,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-71,76; 159,17</t>
+          <t>-62,16; 529,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-87,41; -9,33</t>
+          <t>-88,49; -19,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-78,86; 10,63</t>
+          <t>-76,75; 19,14</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-53,27; 124,24</t>
+          <t>-56,23; 111,17</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4,39</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,58</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,59</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-0,73</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,83</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2,47</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4,39</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-1,58</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>4,02</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,34</t>
+          <t>2,26</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 2,31</t>
+          <t>-0,45; 8,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 4,01</t>
+          <t>-5,22; 2,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 6,74</t>
+          <t>-3,26; 5,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,44; 9,45</t>
+          <t>-3,72; 2,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 2,4</t>
+          <t>-2,45; 3,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 5,06</t>
+          <t>0,39; 8,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 4,73</t>
+          <t>-0,66; 4,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 2,01</t>
+          <t>-2,82; 2,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 4,72</t>
+          <t>-0,75; 5,61</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>69,9%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-25,08%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>9,32%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-17,6%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>19,96%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>59,24%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>69,9%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-25,08%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>43,2%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-67,8; 95,07</t>
+          <t>-5,44; 192,79</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-39,7; 155,35</t>
+          <t>-64,29; 55,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-24,55; 227,99</t>
+          <t>-44,76; 119,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,53; 217,86</t>
+          <t>-66,41; 112,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-64,15; 55,3</t>
+          <t>-43,59; 161,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-48,09; 118,12</t>
+          <t>-2,76; 287,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 128,74</t>
+          <t>-11,84; 121,88</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-44,19; 54,73</t>
+          <t>-43,51; 52,05</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-21,52; 126,59</t>
+          <t>-12,85; 138,31</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,84</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,19</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5,96</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,92</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-2,21</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-3,39</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,84</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-0,19</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,0</t>
+          <t>-3,16</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2,53</t>
+          <t>1,89</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 6,24</t>
+          <t>-3,72; 5,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 3,04</t>
+          <t>-4,55; 3,63</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 1,83</t>
+          <t>0,88; 11,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 5,32</t>
+          <t>-4,85; 6,66</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 4,39</t>
+          <t>-7,52; 2,67</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,33; 13,0</t>
+          <t>-9,08; 1,47</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 4,87</t>
+          <t>-2,52; 4,68</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 2,26</t>
+          <t>-4,44; 1,92</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 6,75</t>
+          <t>-2,11; 5,6</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>18,47%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-4,14%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>130,95%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>12,13%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-29,32%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-44,9%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>18,47%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-4,14%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>153,8%</t>
+          <t>-41,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>32,1%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-48,46; 138,1</t>
+          <t>-55,36; 214,71</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-71,16; 80,36</t>
+          <t>-67,41; 139,03</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-81,0; 50,88</t>
+          <t>6,33; 470,17</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-53,54; 222,47</t>
+          <t>-45,96; 150,46</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-67,75; 170,16</t>
+          <t>-72,82; 72,36</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,05; 521,46</t>
+          <t>-80,32; 47,23</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-29,37; 111,62</t>
+          <t>-33,56; 121,34</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-56,39; 58,71</t>
+          <t>-56,84; 47,92</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-16,39; 158,99</t>
+          <t>-29,86; 131,9</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-6,84</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-3,27</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-2,6</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-3,32</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-1,17</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-1,3</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-6,84</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-3,27</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-3,49</t>
+          <t>-1,11</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-2,3</t>
+          <t>-1,84</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-8,37; 1,29</t>
+          <t>-13,44; -0,41</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 4,9</t>
+          <t>-11,08; 4,69</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 3,85</t>
+          <t>-10,79; 5,39</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 0,43</t>
+          <t>-8,86; 1,82</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-11,77; 4,29</t>
+          <t>-6,61; 5,54</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-11,1; 4,49</t>
+          <t>-6,83; 4,7</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-9,35; -0,43</t>
+          <t>-9,22; -0,05</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 2,79</t>
+          <t>-6,86; 2,98</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 1,91</t>
+          <t>-6,46; 3,34</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-62,2%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-29,75%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-23,66%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-68,62%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-24,26%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-26,89%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-62,2%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-29,75%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-31,73%</t>
+          <t>-22,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-29,24%</t>
+          <t>-23,39%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>-91,41; 17,86</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>-77,34; 78,06</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>-75,76; 77,06</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 279,25</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>-88,5; 291,47</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>-91,63; 32,65</t>
-        </is>
-      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-77,78; 65,21</t>
+          <t>-100,0; 393,56</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-73,91; 81,8</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-89,21; 4,56</t>
+          <t>-88,85; 10,37</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-71,78; 51,36</t>
+          <t>-65,9; 57,51</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-70,97; 40,6</t>
+          <t>-63,15; 71,31</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-0,71</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-1,86</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>1,87</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-1,58</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-1,42</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-0,61</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-0,71</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-1,86</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,74</t>
+          <t>-0,04</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,65</t>
+          <t>0,97</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 0,38</t>
+          <t>-2,82; 1,37</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 0,62</t>
+          <t>-3,85; 0,38</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 1,72</t>
+          <t>-0,57; 4,46</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 1,22</t>
+          <t>-3,66; 0,34</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 0,04</t>
+          <t>-3,42; 0,64</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 4,48</t>
+          <t>-2,39; 2,23</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 0,29</t>
+          <t>-2,53; 0,44</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,05; -0,14</t>
+          <t>-3,04; -0,18</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 2,31</t>
+          <t>-0,75; 2,6</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-10,72%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-27,99%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>28,12%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-25,8%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-23,31%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-9,9%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-10,72%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-27,99%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>-0,67%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-52,15; 8,13</t>
+          <t>-37,49; 24,65</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-51,08; 13,27</t>
+          <t>-50,43; 7,93</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-38,28; 35,45</t>
+          <t>-9,11; 77,85</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-37,85; 23,05</t>
+          <t>-49,94; 7,72</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-51,26; 0,74</t>
+          <t>-47,08; 15,84</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 75,78</t>
+          <t>-33,46; 43,33</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-37,4; 5,03</t>
+          <t>-35,19; 8,47</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-42,32; -1,33</t>
+          <t>-43,3; -2,26</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-12,16; 39,8</t>
+          <t>-10,76; 45,87</t>
         </is>
       </c>
     </row>
